--- a/Backtest/02-08-19/S&P500stock_02-08-19period252RS90.xlsx
+++ b/Backtest/02-08-19/S&P500stock_02-08-19period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="76">
   <si>
     <t>Stock</t>
   </si>
@@ -127,100 +127,82 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>SBAC</t>
-  </si>
-  <si>
-    <t>SNPS</t>
-  </si>
-  <si>
-    <t>INTU</t>
-  </si>
-  <si>
-    <t>EL</t>
-  </si>
-  <si>
-    <t>CMG</t>
-  </si>
-  <si>
-    <t>KEYS</t>
-  </si>
-  <si>
-    <t>BALL</t>
-  </si>
-  <si>
-    <t>CDNS</t>
-  </si>
-  <si>
-    <t>LULU</t>
-  </si>
-  <si>
-    <t>CSGP</t>
-  </si>
-  <si>
-    <t>MA</t>
-  </si>
-  <si>
-    <t>PODD</t>
-  </si>
-  <si>
-    <t>ENPH</t>
-  </si>
-  <si>
-    <t>DAY</t>
-  </si>
-  <si>
-    <t>EPAM</t>
-  </si>
-  <si>
-    <t>FICO</t>
-  </si>
-  <si>
-    <t>2019-10-28</t>
-  </si>
-  <si>
-    <t>2019-08-21</t>
-  </si>
-  <si>
-    <t>2019-08-22</t>
-  </si>
-  <si>
-    <t>2019-08-19</t>
-  </si>
-  <si>
-    <t>2019-10-22</t>
-  </si>
-  <si>
-    <t>2019-10-31</t>
-  </si>
-  <si>
-    <t>2019-10-21</t>
-  </si>
-  <si>
-    <t>2019-09-05</t>
-  </si>
-  <si>
-    <t>2019-10-29</t>
-  </si>
-  <si>
-    <t>2019-08-05</t>
-  </si>
-  <si>
-    <t>2019-11-07</t>
-  </si>
-  <si>
-    <t>2019-08-08</t>
-  </si>
-  <si>
-    <t>2019-11-04</t>
-  </si>
-  <si>
-    <t>Real Estate</t>
+    <t>FTNT</t>
+  </si>
+  <si>
+    <t>DXCM</t>
+  </si>
+  <si>
+    <t>MOH</t>
+  </si>
+  <si>
+    <t>BSX</t>
+  </si>
+  <si>
+    <t>MRK</t>
+  </si>
+  <si>
+    <t>AEE</t>
+  </si>
+  <si>
+    <t>NRG</t>
+  </si>
+  <si>
+    <t>ZBRA</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>AES</t>
+  </si>
+  <si>
+    <t>ERIE</t>
+  </si>
+  <si>
+    <t>TSCO</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>2019-05-02</t>
+  </si>
+  <si>
+    <t>2019-02-21</t>
+  </si>
+  <si>
+    <t>2019-02-11</t>
+  </si>
+  <si>
+    <t>2019-04-24</t>
+  </si>
+  <si>
+    <t>2019-04-30</t>
+  </si>
+  <si>
+    <t>2019-02-14</t>
+  </si>
+  <si>
+    <t>2019-02-28</t>
+  </si>
+  <si>
+    <t>2019-05-23</t>
+  </si>
+  <si>
+    <t>2019-02-27</t>
+  </si>
+  <si>
+    <t>2019-04-25</t>
   </si>
   <si>
     <t>Technology</t>
   </si>
   <si>
-    <t>Consumer Defensive</t>
+    <t>Healthcare</t>
+  </si>
+  <si>
+    <t>Utilities</t>
   </si>
   <si>
     <t>Consumer Cyclical</t>
@@ -229,46 +211,37 @@
     <t>Financial Services</t>
   </si>
   <si>
-    <t>Healthcare</t>
-  </si>
-  <si>
-    <t>REIT - Specialty</t>
-  </si>
-  <si>
     <t>Software - Infrastructure</t>
   </si>
   <si>
-    <t>Software - Application</t>
-  </si>
-  <si>
-    <t>Household &amp; Personal Products</t>
-  </si>
-  <si>
-    <t>Restaurants</t>
-  </si>
-  <si>
-    <t>Scientific &amp; Technical Instruments</t>
-  </si>
-  <si>
-    <t>Packaging &amp; Containers</t>
-  </si>
-  <si>
-    <t>Apparel Retail</t>
-  </si>
-  <si>
-    <t>Real Estate Services</t>
-  </si>
-  <si>
-    <t>Credit Services</t>
-  </si>
-  <si>
     <t>Medical Devices</t>
   </si>
   <si>
-    <t>Solar</t>
-  </si>
-  <si>
-    <t>Information Technology Services</t>
+    <t>Healthcare Plans</t>
+  </si>
+  <si>
+    <t>Drug Manufacturers - General</t>
+  </si>
+  <si>
+    <t>Utilities - Regulated Electric</t>
+  </si>
+  <si>
+    <t>Utilities - Independent Power Producers</t>
+  </si>
+  <si>
+    <t>Communication Equipment</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Utilities - Diversified</t>
+  </si>
+  <si>
+    <t>Insurance Brokers</t>
+  </si>
+  <si>
+    <t>Specialty Retail</t>
   </si>
 </sst>
 </file>
@@ -626,7 +599,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK17"/>
+  <dimension ref="A1:AK13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -747,46 +720,46 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>97.14867617107943</v>
+        <v>98.55670103092784</v>
       </c>
       <c r="C2">
-        <v>426</v>
+        <v>27</v>
       </c>
       <c r="D2">
-        <v>246.79</v>
+        <v>15.87</v>
       </c>
       <c r="E2">
-        <v>1.33</v>
+        <v>1.95</v>
       </c>
       <c r="F2">
-        <v>-0.2428704134587908</v>
+        <v>0.5333577912563824</v>
       </c>
       <c r="G2">
-        <v>1.35</v>
+        <v>2.66</v>
       </c>
       <c r="H2">
-        <v>-0.571722832817226</v>
+        <v>0.4841968939915705</v>
       </c>
       <c r="I2">
-        <v>242.8859985351563</v>
+        <v>16.06359958648682</v>
       </c>
       <c r="J2">
-        <v>235.5649993896484</v>
+        <v>14.9654999256134</v>
       </c>
       <c r="K2">
-        <v>227.477200012207</v>
+        <v>14.53919996261597</v>
       </c>
       <c r="L2">
-        <v>192.3853502655029</v>
+        <v>14.42963998317719</v>
       </c>
       <c r="M2">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="N2">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="P2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="Q2">
         <v>0</v>
@@ -798,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>2.777777777777778</v>
+        <v>0</v>
       </c>
       <c r="U2" t="b">
         <v>0</v>
@@ -810,46 +783,46 @@
         <v>0</v>
       </c>
       <c r="X2">
-        <v>146.13</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="Y2">
-        <v>249.05</v>
+        <v>18.87</v>
       </c>
       <c r="Z2">
-        <v>25.84</v>
+        <v>12.27</v>
       </c>
       <c r="AA2">
-        <v>-795.85</v>
+        <v>1933.59</v>
       </c>
       <c r="AB2">
-        <v>202.63</v>
+        <v>360.47</v>
       </c>
       <c r="AC2">
-        <v>100</v>
+        <v>336</v>
       </c>
       <c r="AD2">
-        <v>-0.96</v>
+        <v>18.34</v>
       </c>
       <c r="AE2">
-        <v>21.74</v>
+        <v>211.43</v>
       </c>
       <c r="AF2">
-        <v>-54</v>
+        <v>20.69</v>
       </c>
       <c r="AG2">
-        <v>257.14</v>
+        <v>16</v>
       </c>
       <c r="AH2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="AI2" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="AJ2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="AK2">
-        <v>71.13729585772228</v>
+        <v>64.40417101755291</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -857,46 +830,46 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>95.5193482688391</v>
+        <v>99.79381443298969</v>
       </c>
       <c r="C3">
-        <v>440</v>
+        <v>183</v>
       </c>
       <c r="D3">
-        <v>132.52</v>
+        <v>35.99</v>
       </c>
       <c r="E3">
-        <v>0.76</v>
+        <v>1.86</v>
       </c>
       <c r="F3">
-        <v>-0.6202091137559242</v>
+        <v>0.4015439664149882</v>
       </c>
       <c r="G3">
-        <v>1.54</v>
+        <v>3.51</v>
       </c>
       <c r="H3">
-        <v>-0.3579420933628145</v>
+        <v>1.584154203281996</v>
       </c>
       <c r="I3">
-        <v>134.7899993896484</v>
+        <v>36.20650100708008</v>
       </c>
       <c r="J3">
-        <v>135.9540008544922</v>
+        <v>36.19362545013428</v>
       </c>
       <c r="K3">
-        <v>128.6302006530762</v>
+        <v>32.72155017852783</v>
       </c>
       <c r="L3">
-        <v>107.0809501266479</v>
+        <v>29.64056253433228</v>
       </c>
       <c r="M3">
-        <v>0.99</v>
+        <v>1</v>
       </c>
       <c r="N3">
-        <v>1.05</v>
+        <v>1.11</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3">
         <v>0</v>
@@ -908,10 +881,10 @@
         <v>0</v>
       </c>
       <c r="T3">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="b">
         <v>0</v>
@@ -920,46 +893,46 @@
         <v>1</v>
       </c>
       <c r="X3">
-        <v>79.14</v>
+        <v>13.23</v>
       </c>
       <c r="Y3">
-        <v>138.72</v>
+        <v>38.17</v>
       </c>
       <c r="Z3">
-        <v>18.63</v>
+        <v>12.92</v>
       </c>
       <c r="AA3">
-        <v>20.66</v>
+        <v>-134.43</v>
       </c>
       <c r="AB3">
-        <v>240.34</v>
+        <v>173.13</v>
       </c>
       <c r="AC3">
-        <v>49.06</v>
+        <v>630</v>
       </c>
       <c r="AD3">
-        <v>3.02</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="AE3">
-        <v>-23.3</v>
+        <v>55.88</v>
       </c>
       <c r="AF3">
-        <v>-39.41</v>
+        <v>221.43</v>
       </c>
       <c r="AG3">
-        <v>220.75</v>
+        <v>-180</v>
       </c>
       <c r="AH3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="AI3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="AJ3" t="s">
-        <v>73</v>
+        <v>66</v>
       </c>
       <c r="AK3">
-        <v>67.5814759791061</v>
+        <v>60.41607870490259</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -967,46 +940,46 @@
         <v>39</v>
       </c>
       <c r="B4">
-        <v>90.83503054989816</v>
+        <v>97.9381443298969</v>
       </c>
       <c r="C4">
-        <v>383</v>
+        <v>444</v>
       </c>
       <c r="D4">
-        <v>277.96</v>
+        <v>137.8</v>
       </c>
       <c r="E4">
-        <v>0.75</v>
+        <v>1.45</v>
       </c>
       <c r="F4">
-        <v>-0.6268290909541196</v>
+        <v>-0.1989412356402527</v>
       </c>
       <c r="G4">
-        <v>1.57</v>
+        <v>3.27</v>
       </c>
       <c r="H4">
-        <v>-0.3241872397647494</v>
+        <v>1.273578021835288</v>
       </c>
       <c r="I4">
-        <v>280.0019958496094</v>
+        <v>137.9740020751953</v>
       </c>
       <c r="J4">
-        <v>278.9654983520508</v>
+        <v>135.3825012207031</v>
       </c>
       <c r="K4">
-        <v>265.1585998535156</v>
+        <v>129.1932005310059</v>
       </c>
       <c r="L4">
-        <v>237.0369001770019</v>
+        <v>119.8574500274658</v>
       </c>
       <c r="M4">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N4">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="P4">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q4">
         <v>0</v>
@@ -1018,58 +991,58 @@
         <v>0</v>
       </c>
       <c r="T4">
-        <v>1.666666666666667</v>
+        <v>0</v>
       </c>
       <c r="U4" t="b">
         <v>1</v>
       </c>
       <c r="V4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4">
-        <v>182.61</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="Y4">
-        <v>284.97</v>
+        <v>154.06</v>
       </c>
       <c r="Z4">
-        <v>66.28</v>
+        <v>10.1</v>
       </c>
       <c r="AA4">
-        <v>12.35</v>
+        <v>24.96</v>
       </c>
       <c r="AB4">
-        <v>12.97</v>
+        <v>136.76</v>
       </c>
       <c r="AC4">
-        <v>3633.33</v>
+        <v>169.25</v>
       </c>
       <c r="AD4">
-        <v>33.86</v>
+        <v>12.62</v>
       </c>
       <c r="AE4">
-        <v>626.03</v>
+        <v>-2.13</v>
       </c>
       <c r="AF4">
-        <v>461.54</v>
+        <v>83.8</v>
       </c>
       <c r="AG4">
-        <v>186.67</v>
+        <v>138.49</v>
       </c>
       <c r="AH4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="AI4" t="s">
+        <v>61</v>
+      </c>
+      <c r="AJ4" t="s">
         <v>67</v>
       </c>
-      <c r="AJ4" t="s">
-        <v>74</v>
-      </c>
       <c r="AK4">
-        <v>54.63315437372388</v>
+        <v>48.01502771416363</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1077,49 +1050,49 @@
         <v>40</v>
       </c>
       <c r="B5">
-        <v>90.22403258655804</v>
+        <v>96.28865979381443</v>
       </c>
       <c r="C5">
-        <v>344</v>
+        <v>56</v>
       </c>
       <c r="D5">
-        <v>182.76</v>
+        <v>38.85</v>
       </c>
       <c r="E5">
-        <v>0.89</v>
+        <v>1.41</v>
       </c>
       <c r="F5">
-        <v>-0.5341494101793851</v>
+        <v>-0.2575251577919836</v>
       </c>
       <c r="G5">
-        <v>1.09</v>
+        <v>2.38</v>
       </c>
       <c r="H5">
-        <v>-0.8642648973337893</v>
+        <v>0.1218580156370767</v>
       </c>
       <c r="I5">
-        <v>187.7719970703125</v>
+        <v>38.24599990844727</v>
       </c>
       <c r="J5">
-        <v>187.7424980163574</v>
+        <v>37.22249984741211</v>
       </c>
       <c r="K5">
-        <v>180.414599609375</v>
+        <v>36.03079978942871</v>
       </c>
       <c r="L5">
-        <v>156.0659999084473</v>
+        <v>34.5838500213623</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N5">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R5">
         <v>0</v>
@@ -1128,58 +1101,58 @@
         <v>0</v>
       </c>
       <c r="T5">
-        <v>2.222222222222222</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W5" t="b">
         <v>0</v>
       </c>
       <c r="X5">
-        <v>121.47</v>
+        <v>25.04</v>
       </c>
       <c r="Y5">
-        <v>194.74</v>
+        <v>39.44</v>
       </c>
       <c r="Z5">
-        <v>60.97</v>
+        <v>49.53</v>
       </c>
       <c r="AA5">
-        <v>8.82</v>
+        <v>242000</v>
       </c>
       <c r="AB5">
-        <v>37.19</v>
+        <v>303.33</v>
       </c>
       <c r="AC5">
-        <v>200</v>
+        <v>27.27</v>
       </c>
       <c r="AD5">
-        <v>12.06</v>
+        <v>4.42</v>
       </c>
       <c r="AE5">
-        <v>-3.16</v>
+        <v>-9.68</v>
       </c>
       <c r="AF5">
-        <v>16.18</v>
+        <v>-22.5</v>
       </c>
       <c r="AG5">
-        <v>166.67</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="AH5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="AI5" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="AJ5" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="AK5">
-        <v>52.66181808422846</v>
+        <v>45.19121363297443</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1187,46 +1160,46 @@
         <v>41</v>
       </c>
       <c r="B6">
-        <v>99.18533604887983</v>
+        <v>93.60824742268041</v>
       </c>
       <c r="C6">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="D6">
-        <v>15.81</v>
+        <v>73.3</v>
       </c>
       <c r="E6">
-        <v>1.72</v>
+        <v>1.26</v>
       </c>
       <c r="F6">
-        <v>0.01530869727082673</v>
+        <v>-0.477214865860974</v>
       </c>
       <c r="G6">
-        <v>1.73</v>
+        <v>1.41</v>
       </c>
       <c r="H6">
-        <v>-0.1441613539084029</v>
+        <v>-1.133387384376704</v>
       </c>
       <c r="I6">
-        <v>15.92039985656738</v>
+        <v>73.41221313476562</v>
       </c>
       <c r="J6">
-        <v>15.27028994560242</v>
+        <v>71.53387413024902</v>
       </c>
       <c r="K6">
-        <v>14.61010000228882</v>
+        <v>72.15496185302734</v>
       </c>
       <c r="L6">
-        <v>12.13014401197433</v>
+        <v>65.34379762649536</v>
       </c>
       <c r="M6">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N6">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="P6">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6">
         <v>0</v>
@@ -1238,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="T6">
-        <v>1.111111111111111</v>
+        <v>0</v>
       </c>
       <c r="U6" t="b">
         <v>0</v>
@@ -1250,46 +1223,46 @@
         <v>1</v>
       </c>
       <c r="X6">
-        <v>7.66</v>
+        <v>50.41</v>
       </c>
       <c r="Y6">
-        <v>16.24</v>
+        <v>76.52</v>
       </c>
       <c r="Z6">
-        <v>20.74</v>
+        <v>195.33</v>
       </c>
       <c r="AA6">
-        <v>36.43</v>
+        <v>10.92</v>
       </c>
       <c r="AB6">
-        <v>20.67</v>
+        <v>103.48</v>
       </c>
       <c r="AC6">
-        <v>139.42</v>
+        <v>159.26</v>
       </c>
       <c r="AD6">
-        <v>5.92</v>
+        <v>6.61</v>
       </c>
       <c r="AE6">
-        <v>3.14</v>
+        <v>-4.11</v>
       </c>
       <c r="AF6">
-        <v>174.14</v>
+        <v>14.06</v>
       </c>
       <c r="AG6">
-        <v>-15.33</v>
+        <v>137.04</v>
       </c>
       <c r="AH6" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="AI6" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="AJ6" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="AK6">
-        <v>42.41166893305001</v>
+        <v>44.3125457664751</v>
       </c>
     </row>
     <row r="7" spans="1:37">
@@ -1297,46 +1270,46 @@
         <v>42</v>
       </c>
       <c r="B7">
-        <v>96.33401221995926</v>
+        <v>90.30927835051547</v>
       </c>
       <c r="C7">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="D7">
-        <v>89.59</v>
+        <v>69.72</v>
       </c>
       <c r="E7">
-        <v>1.82</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="F7">
-        <v>0.08150846925278002</v>
+        <v>-0.9458862430748206</v>
       </c>
       <c r="G7">
-        <v>2.75</v>
+        <v>1.33</v>
       </c>
       <c r="H7">
-        <v>1.003503668425807</v>
+        <v>-1.236912778192273</v>
       </c>
       <c r="I7">
-        <v>90.2759994506836</v>
+        <v>69.05799865722656</v>
       </c>
       <c r="J7">
-        <v>89.84850006103515</v>
+        <v>67.66999969482421</v>
       </c>
       <c r="K7">
-        <v>85.47039993286133</v>
+        <v>67.39579986572265</v>
       </c>
       <c r="L7">
-        <v>76.52535020828248</v>
+        <v>63.4016499710083</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7">
         <v>0</v>
@@ -1348,58 +1321,58 @@
         <v>0</v>
       </c>
       <c r="T7">
-        <v>0.5555555555555555</v>
+        <v>0</v>
       </c>
       <c r="U7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7">
-        <v>53.21</v>
+        <v>52.57</v>
       </c>
       <c r="Y7">
-        <v>94.52</v>
+        <v>70.95</v>
       </c>
       <c r="Z7">
-        <v>16.62</v>
+        <v>15.57</v>
       </c>
       <c r="AA7">
-        <v>9.640000000000001</v>
+        <v>-4.43</v>
       </c>
       <c r="AB7">
-        <v>29.2</v>
+        <v>23.14</v>
       </c>
       <c r="AC7">
-        <v>26.56</v>
+        <v>708.33</v>
       </c>
       <c r="AD7">
-        <v>5.47</v>
+        <v>4.6</v>
       </c>
       <c r="AE7">
-        <v>32.79</v>
+        <v>48.98</v>
       </c>
       <c r="AF7">
-        <v>201.67</v>
+        <v>58.06</v>
       </c>
       <c r="AG7">
-        <v>-193.75</v>
+        <v>358.33</v>
       </c>
       <c r="AH7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AI7" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="AJ7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="AK7">
-        <v>37.49729427561548</v>
+        <v>38.00016571617812</v>
       </c>
     </row>
     <row r="8" spans="1:37">
@@ -1407,49 +1380,49 @@
         <v>43</v>
       </c>
       <c r="B8">
-        <v>99.38900203665987</v>
+        <v>97.73195876288659</v>
       </c>
       <c r="C8">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="D8">
-        <v>74.73999999999999</v>
+        <v>41.57</v>
       </c>
       <c r="E8">
-        <v>1.61</v>
+        <v>1.36</v>
       </c>
       <c r="F8">
-        <v>-0.05751105190932175</v>
+        <v>-0.3307550604816469</v>
       </c>
       <c r="G8">
-        <v>1.32</v>
+        <v>1.97</v>
       </c>
       <c r="H8">
-        <v>-0.605477686415291</v>
+        <v>-0.4087096276677171</v>
       </c>
       <c r="I8">
-        <v>72.68399963378906</v>
+        <v>40.99199981689453</v>
       </c>
       <c r="J8">
-        <v>71.14849967956543</v>
+        <v>40.67649974822998</v>
       </c>
       <c r="K8">
-        <v>67.79499984741211</v>
+        <v>40.00599990844727</v>
       </c>
       <c r="L8">
-        <v>56.48464986801147</v>
+        <v>35.747350025177</v>
       </c>
       <c r="M8">
+        <v>1.01</v>
+      </c>
+      <c r="N8">
         <v>1.02</v>
       </c>
-      <c r="N8">
-        <v>1.07</v>
-      </c>
       <c r="P8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8">
         <v>0</v>
@@ -1458,58 +1431,58 @@
         <v>0</v>
       </c>
       <c r="T8">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="b">
         <v>1</v>
       </c>
       <c r="W8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8">
-        <v>38</v>
+        <v>23.75</v>
       </c>
       <c r="Y8">
-        <v>76.28</v>
+        <v>43.08</v>
       </c>
       <c r="Z8">
-        <v>23.91</v>
+        <v>11.18</v>
       </c>
       <c r="AA8">
-        <v>6.16</v>
+        <v>3520</v>
       </c>
       <c r="AB8">
-        <v>6.12</v>
+        <v>60.04</v>
       </c>
       <c r="AC8">
-        <v>247.06</v>
+        <v>95.03</v>
       </c>
       <c r="AD8">
-        <v>5.53</v>
+        <v>-30.66</v>
       </c>
       <c r="AE8">
-        <v>68.56999999999999</v>
+        <v>-204.35</v>
       </c>
       <c r="AF8">
-        <v>-22.22</v>
+        <v>-73.86</v>
       </c>
       <c r="AG8">
-        <v>164.71</v>
+        <v>118.22</v>
       </c>
       <c r="AH8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="AI8" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="AJ8" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="AK8">
-        <v>34.0538863031415</v>
+        <v>34.21202692061957</v>
       </c>
     </row>
     <row r="9" spans="1:37">
@@ -1517,49 +1490,49 @@
         <v>44</v>
       </c>
       <c r="B9">
-        <v>98.16700610997964</v>
+        <v>96.90721649484536</v>
       </c>
       <c r="C9">
-        <v>304</v>
+        <v>460</v>
       </c>
       <c r="D9">
-        <v>73.04000000000001</v>
+        <v>176.79</v>
       </c>
       <c r="E9">
-        <v>1.13</v>
+        <v>1.55</v>
       </c>
       <c r="F9">
-        <v>-0.3752699574226974</v>
+        <v>-0.05248143026092559</v>
       </c>
       <c r="G9">
-        <v>1.7</v>
+        <v>2.79</v>
       </c>
       <c r="H9">
-        <v>-0.1779162075064679</v>
+        <v>0.6524256589418709</v>
       </c>
       <c r="I9">
-        <v>74.9500015258789</v>
+        <v>177.6059967041016</v>
       </c>
       <c r="J9">
-        <v>74.69900016784668</v>
+        <v>172.4134986877442</v>
       </c>
       <c r="K9">
-        <v>70.56179977416993</v>
+        <v>166.8025991821289</v>
       </c>
       <c r="L9">
-        <v>57.363099899292</v>
+        <v>160.6740998077393</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
         <v>1.06</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R9">
         <v>0</v>
@@ -1568,58 +1541,58 @@
         <v>0</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>10.55555555555556</v>
       </c>
       <c r="U9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W9" t="b">
         <v>1</v>
       </c>
       <c r="X9">
-        <v>39.08</v>
+        <v>110.48</v>
       </c>
       <c r="Y9">
-        <v>77.08</v>
+        <v>184.75</v>
       </c>
       <c r="Z9">
-        <v>19.9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AA9">
-        <v>86.11</v>
+        <v>10.44</v>
       </c>
       <c r="AB9">
-        <v>34.78</v>
+        <v>764.1799999999999</v>
       </c>
       <c r="AC9">
-        <v>8.33</v>
+        <v>3285.71</v>
       </c>
       <c r="AD9">
-        <v>7.5</v>
+        <v>10.47</v>
       </c>
       <c r="AE9">
-        <v>-11.36</v>
+        <v>80.92</v>
       </c>
       <c r="AF9">
-        <v>22.22</v>
+        <v>-35.78</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>2814.29</v>
       </c>
       <c r="AH9" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="AI9" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="AJ9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="AK9">
-        <v>33.39782324032833</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:37">
@@ -1627,46 +1600,46 @@
         <v>45</v>
       </c>
       <c r="B10">
-        <v>96.5376782077393</v>
+        <v>96.49484536082474</v>
       </c>
       <c r="C10">
-        <v>374</v>
+        <v>63</v>
       </c>
       <c r="D10">
-        <v>185.45</v>
+        <v>23.45</v>
       </c>
       <c r="E10">
-        <v>1.31</v>
+        <v>3.53</v>
       </c>
       <c r="F10">
-        <v>-0.2561103678551815</v>
+        <v>2.847422716249749</v>
       </c>
       <c r="G10">
-        <v>1.83</v>
+        <v>3.09</v>
       </c>
       <c r="H10">
-        <v>-0.03164517524818613</v>
+        <v>1.040645885750257</v>
       </c>
       <c r="I10">
-        <v>190.2019989013672</v>
+        <v>23.42600021362305</v>
       </c>
       <c r="J10">
-        <v>188.5415016174316</v>
+        <v>20.90108318328857</v>
       </c>
       <c r="K10">
-        <v>180.7516012573242</v>
+        <v>20.9848331451416</v>
       </c>
       <c r="L10">
-        <v>155.4579503631592</v>
+        <v>19.52198327064514</v>
       </c>
       <c r="M10">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N10">
-        <v>1.05</v>
+        <v>1.12</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
         <v>0</v>
@@ -1675,61 +1648,61 @@
         <v>0</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>3.888888888888889</v>
       </c>
       <c r="U10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10" t="b">
         <v>0</v>
       </c>
       <c r="X10">
-        <v>110.71</v>
+        <v>14.3</v>
       </c>
       <c r="Y10">
-        <v>194.25</v>
+        <v>24.48</v>
       </c>
       <c r="Z10">
-        <v>23.16</v>
+        <v>3.76</v>
       </c>
       <c r="AA10">
-        <v>17.83</v>
+        <v>296320</v>
       </c>
       <c r="AB10">
-        <v>30.38</v>
+        <v>185.86</v>
       </c>
       <c r="AC10">
-        <v>4.23</v>
+        <v>921.1799999999999</v>
       </c>
       <c r="AD10">
-        <v>7.07</v>
+        <v>19.29</v>
       </c>
       <c r="AE10">
-        <v>-55.42</v>
+        <v>170.67</v>
       </c>
       <c r="AF10">
-        <v>133.8</v>
+        <v>348.95</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>-251.55</v>
       </c>
       <c r="AH10" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="AI10" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="AJ10" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="AK10">
-        <v>28.6041009014878</v>
+        <v>67.72387782308226</v>
       </c>
     </row>
     <row r="11" spans="1:37">
@@ -1737,46 +1710,49 @@
         <v>46</v>
       </c>
       <c r="B11">
-        <v>94.29735234215886</v>
+        <v>97.52577319587628</v>
       </c>
       <c r="C11">
-        <v>222</v>
+        <v>114</v>
       </c>
       <c r="D11">
-        <v>60.62</v>
+        <v>17.11</v>
       </c>
       <c r="E11">
-        <v>2.07</v>
+        <v>1.04</v>
       </c>
       <c r="F11">
-        <v>0.2470078992076629</v>
+        <v>-0.7994264376954935</v>
       </c>
       <c r="G11">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="H11">
-        <v>-0.2229226789705546</v>
+        <v>-0.7839891802491568</v>
       </c>
       <c r="I11">
-        <v>62.10039978027343</v>
+        <v>16.91000022888183</v>
       </c>
       <c r="J11">
-        <v>59.48674964904785</v>
+        <v>16.00750007629394</v>
       </c>
       <c r="K11">
-        <v>56.10301979064941</v>
+        <v>15.42020002365112</v>
       </c>
       <c r="L11">
-        <v>45.03293992996216</v>
+        <v>14.02955000400543</v>
       </c>
       <c r="M11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N11">
-        <v>1.11</v>
+        <v>1.1</v>
+      </c>
+      <c r="O11" t="s">
+        <v>49</v>
       </c>
       <c r="P11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q11">
         <v>0</v>
@@ -1788,55 +1764,58 @@
         <v>0</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.666666666666667</v>
       </c>
       <c r="U11" t="b">
         <v>0</v>
       </c>
       <c r="V11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="b">
         <v>1</v>
       </c>
       <c r="X11">
-        <v>31.58</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="Y11">
-        <v>63.82</v>
+        <v>17.13</v>
       </c>
       <c r="Z11">
-        <v>20.29</v>
+        <v>9.31</v>
       </c>
       <c r="AA11">
-        <v>449.04</v>
+        <v>-47.59</v>
       </c>
       <c r="AB11">
-        <v>20.78</v>
+        <v>87.5</v>
       </c>
       <c r="AC11">
-        <v>6.75</v>
+        <v>107.39</v>
+      </c>
+      <c r="AD11">
+        <v>3.36</v>
       </c>
       <c r="AE11">
-        <v>-25.96</v>
+        <v>-65.91</v>
       </c>
       <c r="AF11">
-        <v>2.17</v>
+        <v>-57.69</v>
       </c>
       <c r="AG11">
-        <v>41.1</v>
+        <v>151.23</v>
       </c>
       <c r="AH11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AI11" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="AJ11" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="AK11">
-        <v>25.98258292549474</v>
+        <v>41.05807666348255</v>
       </c>
     </row>
     <row r="12" spans="1:37">
@@ -1844,49 +1823,52 @@
         <v>47</v>
       </c>
       <c r="B12">
-        <v>92.05702647657841</v>
+        <v>94.22680412371133</v>
       </c>
       <c r="C12">
-        <v>147</v>
+        <v>483</v>
       </c>
       <c r="D12">
-        <v>274.16</v>
+        <v>156.15</v>
       </c>
       <c r="E12">
-        <v>0.83</v>
+        <v>1.12</v>
       </c>
       <c r="F12">
-        <v>-0.5738692733685571</v>
+        <v>-0.6822585933920317</v>
       </c>
       <c r="G12">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="H12">
-        <v>-0.6504841578793777</v>
+        <v>-1.14632805860365</v>
       </c>
       <c r="I12">
-        <v>277.6200012207031</v>
+        <v>153.3839996337891</v>
       </c>
       <c r="J12">
-        <v>276.9440017700196</v>
+        <v>144.3970001220703</v>
       </c>
       <c r="K12">
-        <v>266.5484002685547</v>
+        <v>136.961999206543</v>
       </c>
       <c r="L12">
-        <v>228.1834001159668</v>
+        <v>126.1623498535156</v>
       </c>
       <c r="M12">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="N12">
-        <v>1.04</v>
+        <v>1.12</v>
+      </c>
+      <c r="O12" t="s">
+        <v>49</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q12">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -1895,58 +1877,58 @@
         <v>0</v>
       </c>
       <c r="T12">
-        <v>1.111111111111111</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="U12" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" t="b">
         <v>0</v>
       </c>
       <c r="X12">
-        <v>171.89</v>
+        <v>110.15</v>
       </c>
       <c r="Y12">
-        <v>283.33</v>
+        <v>156.58</v>
       </c>
       <c r="Z12">
-        <v>271.14</v>
+        <v>6.67</v>
       </c>
       <c r="AA12">
-        <v>9.75</v>
+        <v>6.5</v>
       </c>
       <c r="AB12">
-        <v>3.32</v>
+        <v>6.18</v>
       </c>
       <c r="AC12">
-        <v>9.84</v>
+        <v>155.88</v>
       </c>
       <c r="AD12">
-        <v>40.68</v>
+        <v>8.73</v>
       </c>
       <c r="AE12">
-        <v>11.05</v>
+        <v>0.58</v>
       </c>
       <c r="AF12">
-        <v>105.68</v>
+        <v>21.83</v>
       </c>
       <c r="AG12">
-        <v>-51.91</v>
+        <v>108.82</v>
       </c>
       <c r="AH12" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="AI12" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="AJ12" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="AK12">
-        <v>7.845511302488823</v>
+        <v>18.92739658811914</v>
       </c>
     </row>
     <row r="13" spans="1:37">
@@ -1954,44 +1936,44 @@
         <v>48</v>
       </c>
       <c r="B13">
-        <v>94.90835030549898</v>
+        <v>92.37113402061856</v>
       </c>
       <c r="C13">
-        <v>466</v>
+        <v>62</v>
       </c>
       <c r="D13">
-        <v>122.56</v>
+        <v>18.15</v>
       </c>
       <c r="E13">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="F13">
-        <v>-0.203150550269619</v>
+        <v>-0.03783544972299287</v>
       </c>
       <c r="G13">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="H13">
-        <v>-0.2904323861666844</v>
+        <v>-0.4475316503485557</v>
       </c>
       <c r="I13">
-        <v>124.0860000610352</v>
+        <v>17.88799934387207</v>
       </c>
       <c r="J13">
-        <v>121.8594997406006</v>
+        <v>17.64749984741211</v>
       </c>
       <c r="K13">
-        <v>117.1847996520996</v>
+        <v>17.53519990921021</v>
       </c>
       <c r="L13">
-        <v>94.33509986877442</v>
+        <v>16.63576996326447</v>
       </c>
       <c r="M13">
+        <v>1.01</v>
+      </c>
+      <c r="N13">
         <v>1.02</v>
       </c>
-      <c r="N13">
-        <v>1.06</v>
-      </c>
       <c r="P13">
         <v>0</v>
       </c>
@@ -1999,504 +1981,64 @@
         <v>0</v>
       </c>
       <c r="R13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <v>0</v>
       </c>
       <c r="T13">
-        <v>4.444444444444444</v>
+        <v>0</v>
       </c>
       <c r="U13" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13">
-        <v>70.8</v>
+        <v>11.65</v>
       </c>
       <c r="Y13">
-        <v>126.71</v>
+        <v>19.53</v>
       </c>
       <c r="Z13">
-        <v>5.81</v>
+        <v>2.06</v>
       </c>
       <c r="AA13">
-        <v>-2.98</v>
+        <v>11.91</v>
       </c>
       <c r="AB13">
-        <v>155.81</v>
+        <v>11.86</v>
       </c>
       <c r="AC13">
-        <v>333.33</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="AD13">
-        <v>1.97</v>
+        <v>8.76</v>
       </c>
       <c r="AE13">
-        <v>-58.82</v>
+        <v>15.63</v>
       </c>
       <c r="AF13">
-        <v>466.67</v>
+        <v>-43.53</v>
       </c>
       <c r="AG13">
-        <v>200</v>
+        <v>198.25</v>
       </c>
       <c r="AH13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="AI13" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="AJ13" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AK13">
-        <v>75.65905963282525</v>
-      </c>
-    </row>
-    <row r="14" spans="1:37">
-      <c r="A14" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14">
-        <v>100</v>
-      </c>
-      <c r="C14">
-        <v>54</v>
-      </c>
-      <c r="D14">
-        <v>30.1</v>
-      </c>
-      <c r="E14">
-        <v>7.15</v>
-      </c>
-      <c r="F14">
-        <v>3.609956315890887</v>
-      </c>
-      <c r="G14">
-        <v>4.86</v>
-      </c>
-      <c r="H14">
-        <v>3.377595038156378</v>
-      </c>
-      <c r="I14">
-        <v>24.37999992370606</v>
-      </c>
-      <c r="J14">
-        <v>21.16849985122681</v>
-      </c>
-      <c r="K14">
-        <v>18.60519994735718</v>
-      </c>
-      <c r="L14">
-        <v>10.41564998865127</v>
-      </c>
-      <c r="M14">
-        <v>1.15</v>
-      </c>
-      <c r="N14">
-        <v>1.31</v>
-      </c>
-      <c r="P14">
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <v>0</v>
-      </c>
-      <c r="R14">
-        <v>0</v>
-      </c>
-      <c r="S14">
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <v>0</v>
-      </c>
-      <c r="U14" t="b">
-        <v>0</v>
-      </c>
-      <c r="V14" t="b">
-        <v>1</v>
-      </c>
-      <c r="W14" t="b">
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <v>3.7</v>
-      </c>
-      <c r="Y14">
-        <v>31.17</v>
-      </c>
-      <c r="Z14">
-        <v>2.38</v>
-      </c>
-      <c r="AA14">
-        <v>-11.34</v>
-      </c>
-      <c r="AB14">
-        <v>143.48</v>
-      </c>
-      <c r="AC14">
-        <v>400</v>
-      </c>
-      <c r="AD14">
-        <v>9.050000000000001</v>
-      </c>
-      <c r="AE14">
-        <v>200</v>
-      </c>
-      <c r="AF14">
-        <v>200</v>
-      </c>
-      <c r="AG14">
-        <v>133.33</v>
-      </c>
-      <c r="AH14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AI14" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>83</v>
-      </c>
-      <c r="AK14">
-        <v>71.57199233040778</v>
-      </c>
-    </row>
-    <row r="15" spans="1:37">
-      <c r="A15" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15">
-        <v>97.75967413441956</v>
-      </c>
-      <c r="C15">
-        <v>358</v>
-      </c>
-      <c r="D15">
-        <v>52.05</v>
-      </c>
-      <c r="E15">
-        <v>1.9</v>
-      </c>
-      <c r="F15">
-        <v>0.1344682868383425</v>
-      </c>
-      <c r="G15">
-        <v>2.21</v>
-      </c>
-      <c r="H15">
-        <v>0.395916303660637</v>
-      </c>
-      <c r="I15">
-        <v>52.44200057983399</v>
-      </c>
-      <c r="J15">
-        <v>50.65099983215332</v>
-      </c>
-      <c r="K15">
-        <v>50.42979995727539</v>
-      </c>
-      <c r="L15">
-        <v>45.02414999961853</v>
-      </c>
-      <c r="M15">
-        <v>1.04</v>
-      </c>
-      <c r="N15">
-        <v>1.04</v>
-      </c>
-      <c r="P15">
-        <v>0</v>
-      </c>
-      <c r="Q15">
-        <v>0</v>
-      </c>
-      <c r="R15">
-        <v>0</v>
-      </c>
-      <c r="S15">
-        <v>0</v>
-      </c>
-      <c r="T15">
-        <v>0</v>
-      </c>
-      <c r="U15" t="b">
-        <v>0</v>
-      </c>
-      <c r="V15" t="b">
-        <v>1</v>
-      </c>
-      <c r="W15" t="b">
-        <v>0</v>
-      </c>
-      <c r="X15">
-        <v>31.39</v>
-      </c>
-      <c r="Y15">
-        <v>56.1</v>
-      </c>
-      <c r="Z15">
-        <v>7.45</v>
-      </c>
-      <c r="AA15">
-        <v>-4.02</v>
-      </c>
-      <c r="AB15">
-        <v>180.95</v>
-      </c>
-      <c r="AC15">
-        <v>33.33</v>
-      </c>
-      <c r="AD15">
-        <v>0.36</v>
-      </c>
-      <c r="AE15">
-        <v>-50</v>
-      </c>
-      <c r="AF15">
-        <v>300</v>
-      </c>
-      <c r="AG15">
-        <v>-33.33</v>
-      </c>
-      <c r="AH15" t="s">
-        <v>63</v>
-      </c>
-      <c r="AI15" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ15" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK15">
-        <v>61.4090458547154</v>
-      </c>
-    </row>
-    <row r="16" spans="1:37">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16">
-        <v>95.72301425661914</v>
-      </c>
-      <c r="C16">
-        <v>479</v>
-      </c>
-      <c r="D16">
-        <v>193.74</v>
-      </c>
-      <c r="E16">
-        <v>1.21</v>
-      </c>
-      <c r="F16">
-        <v>-0.3223101398371347</v>
-      </c>
-      <c r="G16">
-        <v>1.61</v>
-      </c>
-      <c r="H16">
-        <v>-0.2791807683006627</v>
-      </c>
-      <c r="I16">
-        <v>196.9440002441406</v>
-      </c>
-      <c r="J16">
-        <v>193.5805000305176</v>
-      </c>
-      <c r="K16">
-        <v>180.9916000366211</v>
-      </c>
-      <c r="L16">
-        <v>154.1531998825073</v>
-      </c>
-      <c r="M16">
-        <v>1.02</v>
-      </c>
-      <c r="N16">
-        <v>1.09</v>
-      </c>
-      <c r="P16">
-        <v>8</v>
-      </c>
-      <c r="Q16">
-        <v>6</v>
-      </c>
-      <c r="R16">
-        <v>0</v>
-      </c>
-      <c r="S16">
-        <v>0</v>
-      </c>
-      <c r="T16">
-        <v>11.11111111111111</v>
-      </c>
-      <c r="U16" t="b">
-        <v>1</v>
-      </c>
-      <c r="V16" t="b">
-        <v>0</v>
-      </c>
-      <c r="W16" t="b">
-        <v>0</v>
-      </c>
-      <c r="X16">
-        <v>104.77</v>
-      </c>
-      <c r="Y16">
-        <v>201</v>
-      </c>
-      <c r="Z16">
-        <v>9.68</v>
-      </c>
-      <c r="AA16">
-        <v>28.67</v>
-      </c>
-      <c r="AB16">
-        <v>42.07</v>
-      </c>
-      <c r="AC16">
-        <v>19.15</v>
-      </c>
-      <c r="AD16">
-        <v>4.54</v>
-      </c>
-      <c r="AE16">
-        <v>0.9</v>
-      </c>
-      <c r="AF16">
-        <v>-9.02</v>
-      </c>
-      <c r="AG16">
-        <v>29.79</v>
-      </c>
-      <c r="AH16" t="s">
-        <v>64</v>
-      </c>
-      <c r="AI16" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>84</v>
-      </c>
-      <c r="AK16">
-        <v>49.91544658338801</v>
-      </c>
-    </row>
-    <row r="17" spans="1:37">
-      <c r="A17" t="s">
-        <v>52</v>
-      </c>
-      <c r="B17">
-        <v>98.77800407331976</v>
-      </c>
-      <c r="C17">
-        <v>485</v>
-      </c>
-      <c r="D17">
-        <v>359.81</v>
-      </c>
-      <c r="E17">
-        <v>1.28</v>
-      </c>
-      <c r="F17">
-        <v>-0.2759702994497675</v>
-      </c>
-      <c r="G17">
-        <v>1.63</v>
-      </c>
-      <c r="H17">
-        <v>-0.2566775325686196</v>
-      </c>
-      <c r="I17">
-        <v>351.9940063476562</v>
-      </c>
-      <c r="J17">
-        <v>343.9165008544922</v>
-      </c>
-      <c r="K17">
-        <v>320.602001953125</v>
-      </c>
-      <c r="L17">
-        <v>252.8707006072998</v>
-      </c>
-      <c r="M17">
-        <v>1.02</v>
-      </c>
-      <c r="N17">
-        <v>1.1</v>
-      </c>
-      <c r="P17">
-        <v>7</v>
-      </c>
-      <c r="Q17">
-        <v>0</v>
-      </c>
-      <c r="R17">
-        <v>0</v>
-      </c>
-      <c r="S17">
-        <v>0</v>
-      </c>
-      <c r="T17">
-        <v>3.888888888888888</v>
-      </c>
-      <c r="U17" t="b">
-        <v>0</v>
-      </c>
-      <c r="V17" t="b">
-        <v>1</v>
-      </c>
-      <c r="W17" t="b">
-        <v>0</v>
-      </c>
-      <c r="X17">
-        <v>170.26</v>
-      </c>
-      <c r="Y17">
-        <v>371.81</v>
-      </c>
-      <c r="Z17">
-        <v>9.51</v>
-      </c>
-      <c r="AA17">
-        <v>9.01</v>
-      </c>
-      <c r="AB17">
-        <v>2.44</v>
-      </c>
-      <c r="AC17">
-        <v>95.58</v>
-      </c>
-      <c r="AD17">
-        <v>23.91</v>
-      </c>
-      <c r="AE17">
-        <v>92.17</v>
-      </c>
-      <c r="AF17">
-        <v>-16.67</v>
-      </c>
-      <c r="AG17">
-        <v>22.12</v>
-      </c>
-      <c r="AH17" t="s">
-        <v>65</v>
-      </c>
-      <c r="AI17" t="s">
-        <v>67</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>74</v>
-      </c>
-      <c r="AK17">
-        <v>19.09630506209311</v>
+        <v>15.84304014490726</v>
       </c>
     </row>
   </sheetData>
